--- a/frontend/public/templates/student_example.xlsx
+++ b/frontend/public/templates/student_example.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="20475" windowHeight="7500"/>
+    <workbookView windowWidth="20475" windowHeight="8220"/>
   </bookViews>
   <sheets>
     <sheet name="Students" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="303">
   <si>
-    <t>Student ID</t>
+    <t>Student Code</t>
   </si>
   <si>
     <t>Email</t>
@@ -3064,7 +3064,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="B1:C1 A2:C101" numberStoredAsText="1"/>
+    <ignoredError sqref="A2:C101 B1:C1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>